--- a/feedback_forms/003_product_usage_survey_template--feedback_forms.xlsx
+++ b/feedback_forms/003_product_usage_survey_template--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>product_used</t>
+          <t>frequency_of_use_2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Product Used</t>
+          <t>How often do you use this product?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frequency_of_use</t>
+          <t>why_used_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How often do you use this product?</t>
+          <t>Why did you start using this product?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>why_used</t>
+          <t>satisfaction_level_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Why did you start using this product?</t>
+          <t>What is your satisfaction level with this product?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>satisfaction_level</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your satisfaction level with this product?</t>
+          <t>Do you have any feedback for us?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>product_used_at_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Do you have any feedback for us?</t>
+          <t>Product Used at</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>phone_number_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>email_address_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>product_purchase_date</t>
+          <t>product_purchase_date_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>product_usage_date</t>
+          <t>product_usage_date_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>product_used_at</t>
+          <t>frequency_of_use_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Product Used at</t>
+          <t>Frequency Of Use 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>frequency_of_use_2</t>
+          <t>satisfaction_level_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How often do you use this product?</t>
+          <t>Satisfaction Level 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>why_used_2</t>
+          <t>feedback_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Why did you start using this product?</t>
+          <t>Feedback 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>satisfaction_level_2</t>
+          <t>product_used_at_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your satisfaction level with this product?</t>
+          <t>Product Used At 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,274 +814,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>email_address_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Do you have any feedback for us?</t>
+          <t>Email Address 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phone_number_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email_address_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>product_purchase_date_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>When did you purchase this product?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>product_usage_date_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How long have you been using this product?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>product_used_at_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Product Used at</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>frequency_of_use_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How often do you use this product?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>why_used_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Why did you start using this product?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your satisfaction level with this product?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>feedback_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any feedback for us?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>phone_number_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email_address_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1126,714 +873,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>product_used_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>product_used_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>banana</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>banana</t>
+          <t>sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product_used_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>frequently</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>product_used_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>never</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product_used_choices</t>
+          <t>satisfaction_level_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frequency_of_use_choices</t>
+          <t>satisfaction_level_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frequency_of_use_choices</t>
+          <t>satisfaction_level_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frequency_of_use_choices</t>
+          <t>satisfaction_level_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frequency_of_use_choices</t>
+          <t>satisfaction_level_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>product_used_at_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>apple</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>product_used_at_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>banana</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>product_used_at_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>orange</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>product_used_at_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>mango</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>mango</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>satisfaction_level_choices</t>
+          <t>product_used_at_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>product_used_at_choices</t>
+          <t>frequency_of_use_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>rarely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>product_used_at_choices</t>
+          <t>frequency_of_use_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>banana</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>banana</t>
+          <t>sometimes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>product_used_at_choices</t>
+          <t>frequency_of_use_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>orange</t>
+          <t>frequently</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>product_used_at_choices</t>
+          <t>frequency_of_use_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mango</t>
+          <t>never</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>product_used_at_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>satisfaction_level_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>satisfaction_level_2_choices</t>
+          <t>product_used_at_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>apple</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>satisfaction_level_2_choices</t>
+          <t>product_used_at_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>banana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>banana</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>satisfaction_level_2_choices</t>
+          <t>product_used_at_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>orange</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>orange</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>satisfaction_level_2_choices</t>
+          <t>product_used_at_3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>mango</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>mango</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>satisfaction_level_2_choices</t>
+          <t>product_used_at_3_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>product_used_at_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>product_used_at_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>banana</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>banana</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>product_used_at_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>product_used_at_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>mango</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>mango</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>product_used_at_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
           <t>other</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>frequency_of_use_3_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>frequency_of_use_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>frequency_of_use_3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>frequently</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>frequently</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>frequency_of_use_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>satisfaction_level_3_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
         </is>
       </c>
     </row>
